--- a/data/评测报告.xlsx
+++ b/data/评测报告.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +28,19 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -56,9 +69,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,9 +517,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -614,16 +628,13 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
           <t>混淆矩阵</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>物流慢</t>
@@ -651,7 +662,6 @@
           <t>物流慢</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>25</v>
       </c>
@@ -671,7 +681,6 @@
           <t>质量差</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
@@ -691,7 +700,6 @@
           <t>货不对版</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
@@ -711,7 +719,6 @@
           <t>客服态度差</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
@@ -724,6 +731,142 @@
       <c r="F18" t="n">
         <v>22</v>
       </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>方法对比</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>准确率</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>宏F1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>关键词兜底</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>93.0%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0.930</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>mock按关键词造，关键词最准</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>bge短标签</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>73.0%</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>标签“物流慢”4字太泛</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>bge描述句</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>86.0%</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>标签改为描述句，提升13%</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>混合(描述句+关键词)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>88.0%</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>bge&gt;0.62用bge否则关键词，扬长避短</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>当前采用：混合策略（关键词93%兜底 + bge描述句88%泛化），mock上88%，真数据上bge更稳</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
